--- a/artfynd/A 50775-2025 artfynd.xlsx
+++ b/artfynd/A 50775-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ60"/>
+  <dimension ref="A1:AZ61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6957,48 +6957,60 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>5145134</v>
+        <v>137281112</v>
       </c>
       <c r="B56" t="n">
-        <v>100798</v>
+        <v>98256</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222617</v>
+        <v>221945</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) H. Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>norra vägskärningen av Södra Tvärvägen O om Mossvägen, Vg</t>
+          <t>Falevi ny ÅVC, Hulesjön, Falköping, Vg</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>413466</v>
+        <v>413727</v>
       </c>
       <c r="R56" t="n">
-        <v>6446513</v>
+        <v>6446484</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7022,17 +7034,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2010-08-21</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2010-08-21</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>flera fina tuvor</t>
+          <t>Flytt av revlummer till skogsområde S Hulesjön pga ny detaljplan.Efter flytt finns revlummer ej kvar på platsen.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7041,30 +7053,31 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Jörgen Grahn</t>
+          <t>Dag Fredriksson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jörgen Grahn</t>
+          <t>Dag Fredriksson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5145134</t>
+          <t>https://artportalen.se/Sighting/137281112</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>60510220</v>
+        <v>5145134</v>
       </c>
       <c r="B57" t="n">
         <v>100798</v>
@@ -7095,14 +7108,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>N vägskärningen, S Tvärvägen O om Mossvägen, Vg</t>
+          <t>norra vägskärningen av Södra Tvärvägen O om Mossvägen, Vg</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>413496</v>
+        <v>413466</v>
       </c>
       <c r="R57" t="n">
-        <v>6446503</v>
+        <v>6446513</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7129,17 +7142,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2016-06-25</t>
+          <t>2010-08-21</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2016-06-25</t>
+          <t>2010-08-21</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>talrik blommande, alla kortväxta</t>
+          <t>flera fina tuvor</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7165,54 +7178,54 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60510220</t>
+          <t>https://artportalen.se/Sighting/5145134</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134145363</v>
+        <v>60510220</v>
       </c>
       <c r="B58" t="n">
-        <v>103482</v>
+        <v>100798</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>223246</v>
+        <v>222617</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Phleum phleoides</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(L.) H. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Falevi, Vg</t>
+          <t>N vägskärningen, S Tvärvägen O om Mossvägen, Vg</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>413493</v>
+        <v>413496</v>
       </c>
       <c r="R58" t="n">
-        <v>6446678</v>
+        <v>6446503</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7236,12 +7249,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2016-06-25</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2016-06-25</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>talrik blommande, alla kortväxta</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7250,77 +7268,71 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Alfred Olofsson</t>
+          <t>Jörgen Grahn</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
+          <t>Jörgen Grahn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134145363</t>
+          <t>https://artportalen.se/Sighting/60510220</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>5893253</v>
+        <v>134145363</v>
       </c>
       <c r="B59" t="n">
-        <v>99029</v>
+        <v>103482</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>223578</v>
+        <v>223246</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Äkta ängsnycklar</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. incarnata</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Södra Tvärvägen SO om Hulesjön, Vg</t>
+          <t>Falevi, Vg</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>413463</v>
+        <v>413493</v>
       </c>
       <c r="R59" t="n">
-        <v>6446512</v>
+        <v>6446678</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7344,17 +7356,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2003-06-26</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2003-06-26</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>2 ex</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7363,30 +7370,31 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
+          <t>Alfred Olofsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
+          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5893253</t>
+          <t>https://artportalen.se/Sighting/134145363</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>5901890</v>
+        <v>5893253</v>
       </c>
       <c r="B60" t="n">
         <v>99029</v>
@@ -7410,20 +7418,29 @@
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>norra vägskärningen av Södra Tvärvägen O om Mossvägen, Vg</t>
+          <t>Södra Tvärvägen SO om Hulesjön, Vg</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>413466</v>
+        <v>413463</v>
       </c>
       <c r="R60" t="n">
-        <v>6446513</v>
+        <v>6446512</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7447,17 +7464,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2010-08-21</t>
+          <t>2003-06-26</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2010-08-21</t>
+          <t>2003-06-26</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>22 eller något fler nere i vägdiket</t>
+          <t>2 ex</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7472,16 +7489,119 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Jörgen Grahn</t>
+          <t>Jonas F Grahn</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Jörgen Grahn</t>
+          <t>Jonas F Grahn</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5893253</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>5901890</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99029</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>223578</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Äkta ängsnycklar</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Dactylorhiza incarnata var. incarnata</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>norra vägskärningen av Södra Tvärvägen O om Mossvägen, Vg</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>413466</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6446513</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Luttra</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2010-08-21</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2010-08-21</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>22 eller något fler nere i vägdiket</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/5901890</t>
         </is>
@@ -7548,6 +7668,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50775-2025 artfynd.xlsx
+++ b/artfynd/A 50775-2025 artfynd.xlsx
@@ -6960,7 +6960,7 @@
         <v>137281112</v>
       </c>
       <c r="B56" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 50775-2025 artfynd.xlsx
+++ b/artfynd/A 50775-2025 artfynd.xlsx
@@ -6960,7 +6960,7 @@
         <v>137281112</v>
       </c>
       <c r="B56" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 50775-2025 artfynd.xlsx
+++ b/artfynd/A 50775-2025 artfynd.xlsx
@@ -6960,7 +6960,7 @@
         <v>137281112</v>
       </c>
       <c r="B56" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 50775-2025 artfynd.xlsx
+++ b/artfynd/A 50775-2025 artfynd.xlsx
@@ -6960,7 +6960,7 @@
         <v>137281112</v>
       </c>
       <c r="B56" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 50775-2025 artfynd.xlsx
+++ b/artfynd/A 50775-2025 artfynd.xlsx
@@ -6960,7 +6960,7 @@
         <v>137281112</v>
       </c>
       <c r="B56" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 50775-2025 artfynd.xlsx
+++ b/artfynd/A 50775-2025 artfynd.xlsx
@@ -6960,7 +6960,7 @@
         <v>137281112</v>
       </c>
       <c r="B56" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 50775-2025 artfynd.xlsx
+++ b/artfynd/A 50775-2025 artfynd.xlsx
@@ -6960,7 +6960,7 @@
         <v>137281112</v>
       </c>
       <c r="B56" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 50775-2025 artfynd.xlsx
+++ b/artfynd/A 50775-2025 artfynd.xlsx
@@ -6960,7 +6960,7 @@
         <v>137281112</v>
       </c>
       <c r="B56" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 50775-2025 artfynd.xlsx
+++ b/artfynd/A 50775-2025 artfynd.xlsx
@@ -6960,7 +6960,7 @@
         <v>137281112</v>
       </c>
       <c r="B56" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
